--- a/modelo_sentence_similarity/embedding_comparison_results.xlsx
+++ b/modelo_sentence_similarity/embedding_comparison_results.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,40 +441,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Total Tokens</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RAM Proceso (MB)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Tiempo Chunking (s)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tiempo Embedding (s)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MRR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Top_1_Accuracy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Top_3_Accuracy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Precision@3</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Recall@3</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>LLM_Judge_Score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Eficiencia (MRR / T.Emb)</t>
         </is>
@@ -496,28 +501,31 @@
         <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005</v>
+        <v>4240</v>
       </c>
       <c r="F2" t="n">
-        <v>0.52</v>
+        <v>2254.83</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8857</v>
+        <v>0.0009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8571</v>
+        <v>0.54</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2857</v>
+        <v>0.8611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8571</v>
+        <v>0.7778</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6897</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.5969</v>
       </c>
     </row>
     <row r="3">
@@ -536,28 +544,31 @@
         <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002</v>
+        <v>5413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.92</v>
+        <v>2260.33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.0003</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3333</v>
+        <v>0.7751</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0091</v>
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.408</v>
       </c>
     </row>
     <row r="4">
@@ -576,28 +587,31 @@
         <v>111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>9767</v>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>2279.92</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6643</v>
+        <v>0.0003</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3</v>
+        <v>0.3985</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4616</v>
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4302</v>
       </c>
     </row>
     <row r="5">
@@ -616,28 +630,31 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004</v>
+        <v>4222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>2280.51</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6443</v>
+        <v>0.0003</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>0.7778</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>0.6667</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2905</v>
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.6468</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +673,31 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>4692</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>2271</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6061</v>
+        <v>0.0003</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2333</v>
+        <v>0.6792</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5249</v>
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.0956</v>
       </c>
     </row>
     <row r="7">
@@ -696,28 +716,31 @@
         <v>31</v>
       </c>
       <c r="E7" t="n">
+        <v>5682</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2285.39</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.0002</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.5407</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1667</v>
+        <v>0.4833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3171</v>
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.2645</v>
       </c>
     </row>
     <row r="8">
@@ -736,28 +759,31 @@
         <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002</v>
+        <v>4242</v>
       </c>
       <c r="F8" t="n">
-        <v>0.36</v>
+        <v>2293.77</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5958</v>
+        <v>0.0003</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>0.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.25</v>
+        <v>0.6212</v>
       </c>
       <c r="J8" t="n">
-        <v>0.75</v>
+        <v>0.4444</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6477</v>
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.7535</v>
       </c>
     </row>
     <row r="9">
@@ -776,28 +802,31 @@
         <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003</v>
+        <v>4530</v>
       </c>
       <c r="F9" t="n">
-        <v>0.46</v>
+        <v>2296.12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.791</v>
+        <v>0.0002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.22</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0.5673</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7365</v>
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.6386</v>
       </c>
     </row>
     <row r="10">
@@ -816,28 +845,31 @@
         <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0004</v>
+        <v>5080</v>
       </c>
       <c r="F10" t="n">
-        <v>0.33</v>
+        <v>2293.98</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3046</v>
+        <v>0.0003</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1333</v>
+        <v>0.6348</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9104</v>
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.4947</v>
       </c>
     </row>
     <row r="11">
@@ -856,28 +888,31 @@
         <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0007</v>
+        <v>4240</v>
       </c>
       <c r="F11" t="n">
-        <v>0.97</v>
+        <v>2297</v>
       </c>
       <c r="G11" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.0303</v>
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.8747</v>
       </c>
     </row>
     <row r="12">
@@ -896,28 +931,31 @@
         <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0008</v>
+        <v>5413</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>2294.29</v>
       </c>
       <c r="G12" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.4199</v>
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.4097</v>
       </c>
     </row>
     <row r="13">
@@ -936,28 +974,31 @@
         <v>111</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0003</v>
+        <v>9767</v>
       </c>
       <c r="F13" t="n">
-        <v>1.24</v>
+        <v>2308.36</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7333</v>
+        <v>0.0005</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333</v>
+        <v>0.6083</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5937</v>
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6056</v>
       </c>
     </row>
     <row r="14">
@@ -976,28 +1017,31 @@
         <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0009</v>
+        <v>4222</v>
       </c>
       <c r="F14" t="n">
+        <v>2318.47</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.54</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
       <c r="I14" t="n">
-        <v>0.3333</v>
+        <v>0.8519</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.7778</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.8889</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5051</v>
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.5674</v>
       </c>
     </row>
     <row r="15">
@@ -1016,28 +1060,31 @@
         <v>26</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005999999999999999</v>
+        <v>4692</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6899999999999999</v>
+        <v>2389.68</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>0.0002</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3333</v>
+        <v>0.8167</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1666</v>
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="16">
@@ -1056,28 +1103,31 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0005</v>
+        <v>5682</v>
       </c>
       <c r="F16" t="n">
-        <v>0.95</v>
+        <v>2351.66</v>
       </c>
       <c r="G16" t="n">
-        <v>0.87</v>
+        <v>0.0004</v>
       </c>
       <c r="H16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.9</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.9169</v>
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.0071</v>
       </c>
     </row>
     <row r="17">
@@ -1096,28 +1146,31 @@
         <v>16</v>
       </c>
       <c r="E17" t="n">
+        <v>4242</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2391.64</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.0003</v>
       </c>
-      <c r="F17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.875</v>
-      </c>
       <c r="H17" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.4549</v>
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.5826</v>
       </c>
     </row>
     <row r="18">
@@ -1136,28 +1189,31 @@
         <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0003</v>
+        <v>4530</v>
       </c>
       <c r="F18" t="n">
-        <v>0.63</v>
+        <v>2399.36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.95</v>
+        <v>0.0002</v>
       </c>
       <c r="H18" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8167</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.5103</v>
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.4726</v>
       </c>
     </row>
     <row r="19">
@@ -1176,28 +1232,31 @@
         <v>18</v>
       </c>
       <c r="E19" t="n">
+        <v>5080</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2356.25</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.0004</v>
       </c>
-      <c r="F19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.9</v>
-      </c>
       <c r="H19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.2482</v>
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.3017</v>
       </c>
     </row>
     <row r="20">
@@ -1216,28 +1275,31 @@
         <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008</v>
+        <v>4617</v>
       </c>
       <c r="F20" t="n">
-        <v>0.97</v>
+        <v>2435.96</v>
       </c>
       <c r="G20" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.3333</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0288</v>
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.0083</v>
       </c>
     </row>
     <row r="21">
@@ -1256,28 +1318,31 @@
         <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004</v>
+        <v>5919</v>
       </c>
       <c r="F21" t="n">
-        <v>1.25</v>
+        <v>2411.76</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9444</v>
+        <v>0.0003</v>
       </c>
       <c r="H21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.7568</v>
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.7013</v>
       </c>
     </row>
     <row r="22">
@@ -1296,28 +1361,31 @@
         <v>111</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0004</v>
+        <v>10632</v>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2422.16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.55</v>
+        <v>0.0005</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3333</v>
+        <v>0.5144</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2413</v>
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2429</v>
       </c>
     </row>
     <row r="23">
@@ -1336,28 +1404,31 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0003</v>
+        <v>4600</v>
       </c>
       <c r="F23" t="n">
-        <v>0.62</v>
+        <v>2440.02</v>
       </c>
       <c r="G23" t="n">
-        <v>0.599</v>
+        <v>0.0004</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1667</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.8889</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9713000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.7223</v>
       </c>
     </row>
     <row r="24">
@@ -1376,28 +1447,31 @@
         <v>26</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0008</v>
+        <v>5106</v>
       </c>
       <c r="F24" t="n">
-        <v>0.66</v>
+        <v>2438.07</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6811</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2333</v>
+        <v>0.77</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.026</v>
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.3085</v>
       </c>
     </row>
     <row r="25">
@@ -1416,28 +1490,31 @@
         <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0004</v>
+        <v>6174</v>
       </c>
       <c r="F25" t="n">
-        <v>0.84</v>
+        <v>2424.19</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4982</v>
+        <v>0.0003</v>
       </c>
       <c r="H25" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.6</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.5903</v>
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.855</v>
       </c>
     </row>
     <row r="26">
@@ -1456,28 +1533,31 @@
         <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0005</v>
+        <v>4621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.42</v>
+        <v>2441.96</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4562</v>
+        <v>0.0008</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1667</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.7778</v>
       </c>
       <c r="L26" t="n">
-        <v>1.0796</v>
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.4146</v>
       </c>
     </row>
     <row r="27">
@@ -1496,28 +1576,31 @@
         <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0004</v>
+        <v>4952</v>
       </c>
       <c r="F27" t="n">
-        <v>0.41</v>
+        <v>2423.64</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6861</v>
+        <v>0.0005</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2667</v>
+        <v>0.5798</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.6701</v>
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="28">
@@ -1536,28 +1619,31 @@
         <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0019</v>
+        <v>5527</v>
       </c>
       <c r="F28" t="n">
-        <v>0.46</v>
+        <v>2461.35</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3848</v>
+        <v>0.0003</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1333</v>
+        <v>0.58</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8421999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.3421</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,40 +1683,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Total Tokens</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RAM Proceso (MB)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Tiempo Chunking (s)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Tiempo Embedding (s)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MRR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Top_1_Accuracy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Top_3_Accuracy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Precision@3</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Recall@3</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>LLM_Judge_Score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Eficiencia (MRR / T.Emb)</t>
         </is>
@@ -1639,41 +1730,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>intfloat/multilingual-e5-small</t>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>500</v>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008</v>
+        <v>4617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>2435.96</v>
       </c>
       <c r="G2" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.3333</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4199</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.0083</v>
       </c>
     </row>
   </sheetData>
@@ -1687,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1810,16 @@
           <t>Tiempo Embedding (s)</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Tokens</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RAM Proceso (MB)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1724,16 +1828,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8823111111111112</v>
+        <v>0.8103666666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9888888888888889</v>
+        <v>0.9543222222222223</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7822222222222223</v>
+        <v>0.6344444444444445</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5318.666666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2399.36</v>
       </c>
     </row>
     <row r="3">
@@ -1743,16 +1853,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6444222222222222</v>
+        <v>0.7350444444444445</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7864222222222222</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8788888888888889</v>
+        <v>0.8388888888888889</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5794.222222222223</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2461.35</v>
       </c>
     </row>
     <row r="4">
@@ -1762,16 +1878,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6620444444444444</v>
+        <v>0.6442555555555556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.750788888888889</v>
+        <v>0.7839555555555555</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5933333333333333</v>
+        <v>0.4122222222222222</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5318.666666666667</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2296.12</v>
       </c>
     </row>
   </sheetData>

--- a/modelo_sentence_similarity/embedding_comparison_results.xlsx
+++ b/modelo_sentence_similarity/embedding_comparison_results.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Resultados_Completos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mejor_Modelo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Resumen_Por_Modelo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen_Promedios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,50 +435,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nº Chunks</t>
+          <t>Total Tokens</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total Tokens</t>
+          <t>RAM (MB)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>RAM Proceso (MB)</t>
+          <t>T. Chunking (s)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tiempo Chunking (s)</t>
+          <t>T. Embedding (s)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tiempo Embedding (s)</t>
+          <t>MRR</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>MRR</t>
+          <t>Top_1_Acc</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Top_1_Accuracy</t>
+          <t>Top_3_Acc</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Top_3_Accuracy</t>
+          <t>LLM_Judge</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>LLM_Judge_Score</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Eficiencia (MRR / T.Emb)</t>
         </is>
@@ -498,34 +492,31 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>4338</v>
       </c>
       <c r="E2" t="n">
-        <v>4240</v>
+        <v>3444.43</v>
       </c>
       <c r="F2" t="n">
-        <v>2254.83</v>
+        <v>0.0011</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009</v>
+        <v>1.04</v>
       </c>
       <c r="H2" t="n">
-        <v>0.54</v>
+        <v>0.7991</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8611</v>
+        <v>0.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7778</v>
+        <v>0.75</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8889</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.5969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -541,34 +532,31 @@
         <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>5535</v>
       </c>
       <c r="E3" t="n">
-        <v>5413</v>
+        <v>3554.63</v>
       </c>
       <c r="F3" t="n">
-        <v>2260.33</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003</v>
+        <v>1.32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.55</v>
+        <v>0.7405</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7751</v>
+        <v>0.625</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6667</v>
+        <v>0.875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8889</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.408</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -584,34 +572,31 @@
         <v>300</v>
       </c>
       <c r="D4" t="n">
-        <v>111</v>
+        <v>9989</v>
       </c>
       <c r="E4" t="n">
-        <v>9767</v>
+        <v>3542.79</v>
       </c>
       <c r="F4" t="n">
-        <v>2279.92</v>
+        <v>0.0005</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003</v>
+        <v>2.23</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
+        <v>0.4979</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3985</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.4302</v>
       </c>
     </row>
     <row r="5">
@@ -627,34 +612,31 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>4268</v>
       </c>
       <c r="E5" t="n">
-        <v>4222</v>
+        <v>3561.44</v>
       </c>
       <c r="F5" t="n">
-        <v>2280.51</v>
+        <v>0.0003</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0003</v>
+        <v>0.6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.29</v>
+        <v>0.5697</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7778</v>
+        <v>0.4286</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6667</v>
+        <v>0.7143</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8889</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.6468</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -670,34 +652,31 @@
         <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>4744</v>
       </c>
       <c r="E6" t="n">
-        <v>4692</v>
+        <v>3546.12</v>
       </c>
       <c r="F6" t="n">
-        <v>2271</v>
+        <v>0.0004</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003</v>
+        <v>0.77</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.6432</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6792</v>
+        <v>0.5556</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.0956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,34 +692,31 @@
         <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>5744</v>
       </c>
       <c r="E7" t="n">
-        <v>5682</v>
+        <v>3551.39</v>
       </c>
       <c r="F7" t="n">
-        <v>2285.39</v>
+        <v>0.0004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>0.6302</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4833</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -756,34 +732,31 @@
         <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>4274</v>
       </c>
       <c r="E8" t="n">
-        <v>4242</v>
+        <v>3553.65</v>
       </c>
       <c r="F8" t="n">
-        <v>2293.77</v>
+        <v>0.0004</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003</v>
+        <v>0.43</v>
       </c>
       <c r="H8" t="n">
-        <v>0.23</v>
+        <v>0.6056</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6212</v>
+        <v>0.4444</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4444</v>
+        <v>0.6667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8889</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.7535</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -799,34 +772,31 @@
         <v>150</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>4562</v>
       </c>
       <c r="E9" t="n">
-        <v>4530</v>
+        <v>3565.93</v>
       </c>
       <c r="F9" t="n">
-        <v>2296.12</v>
+        <v>0.0005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002</v>
+        <v>0.46</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22</v>
+        <v>0.5579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5673</v>
+        <v>0.4444</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.5556</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2.6386</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -842,34 +812,31 @@
         <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>5116</v>
       </c>
       <c r="E10" t="n">
-        <v>5080</v>
+        <v>3565.94</v>
       </c>
       <c r="F10" t="n">
-        <v>2293.98</v>
+        <v>0.0003</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003</v>
+        <v>0.57</v>
       </c>
       <c r="H10" t="n">
-        <v>0.25</v>
+        <v>0.3043</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6348</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.4947</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -885,34 +852,31 @@
         <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>4338</v>
       </c>
       <c r="E11" t="n">
-        <v>4240</v>
+        <v>3541.09</v>
       </c>
       <c r="F11" t="n">
-        <v>2297</v>
+        <v>0.0005</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003</v>
+        <v>1.14</v>
       </c>
       <c r="H11" t="n">
-        <v>0.47</v>
+        <v>0.8304</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8889</v>
+        <v>0.75</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7778</v>
+        <v>0.875</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.8747</v>
       </c>
     </row>
     <row r="12">
@@ -928,34 +892,31 @@
         <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>5535</v>
       </c>
       <c r="E12" t="n">
-        <v>5413</v>
+        <v>3571.09</v>
       </c>
       <c r="F12" t="n">
-        <v>2294.29</v>
+        <v>0.0004</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0003</v>
+        <v>3.91</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.8125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8519</v>
+        <v>0.625</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7778</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.4097</v>
       </c>
     </row>
     <row r="13">
@@ -971,34 +932,31 @@
         <v>300</v>
       </c>
       <c r="D13" t="n">
-        <v>111</v>
+        <v>9989</v>
       </c>
       <c r="E13" t="n">
-        <v>9767</v>
+        <v>3530.08</v>
       </c>
       <c r="F13" t="n">
-        <v>2308.36</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0005</v>
+        <v>4.49</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.4933</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6083</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.6056</v>
       </c>
     </row>
     <row r="14">
@@ -1014,34 +972,31 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>4268</v>
       </c>
       <c r="E14" t="n">
-        <v>4222</v>
+        <v>3547.25</v>
       </c>
       <c r="F14" t="n">
-        <v>2318.47</v>
+        <v>0.0005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0003</v>
+        <v>1.39</v>
       </c>
       <c r="H14" t="n">
-        <v>0.54</v>
+        <v>0.6786</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8519</v>
+        <v>0.5714</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7778</v>
+        <v>0.7143</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8889</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.5674</v>
       </c>
     </row>
     <row r="15">
@@ -1057,34 +1012,31 @@
         <v>150</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>4744</v>
       </c>
       <c r="E15" t="n">
-        <v>4692</v>
+        <v>3575.49</v>
       </c>
       <c r="F15" t="n">
-        <v>2389.68</v>
+        <v>0.0005</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
-        <v>0.62</v>
+        <v>0.6821</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8167</v>
+        <v>0.5556</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.7778</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.307</v>
       </c>
     </row>
     <row r="16">
@@ -1100,34 +1052,31 @@
         <v>300</v>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>5744</v>
       </c>
       <c r="E16" t="n">
-        <v>5682</v>
+        <v>3629.45</v>
       </c>
       <c r="F16" t="n">
-        <v>2351.66</v>
+        <v>0.0005</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004</v>
+        <v>1.63</v>
       </c>
       <c r="H16" t="n">
-        <v>0.76</v>
+        <v>0.6063</v>
       </c>
       <c r="I16" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.0071</v>
       </c>
     </row>
     <row r="17">
@@ -1143,34 +1092,31 @@
         <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>4274</v>
       </c>
       <c r="E17" t="n">
-        <v>4242</v>
+        <v>3642.78</v>
       </c>
       <c r="F17" t="n">
-        <v>2391.64</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5626</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8889</v>
+        <v>0.4444</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7778</v>
+        <v>0.6667</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.5826</v>
       </c>
     </row>
     <row r="18">
@@ -1186,34 +1132,31 @@
         <v>150</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>4562</v>
       </c>
       <c r="E18" t="n">
-        <v>4530</v>
+        <v>3659.46</v>
       </c>
       <c r="F18" t="n">
-        <v>2399.36</v>
+        <v>0.0004</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002</v>
+        <v>1.37</v>
       </c>
       <c r="H18" t="n">
-        <v>0.55</v>
+        <v>0.6644</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8167</v>
+        <v>0.5556</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.7778</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.4726</v>
       </c>
     </row>
     <row r="19">
@@ -1229,40 +1172,37 @@
         <v>300</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>5116</v>
       </c>
       <c r="E19" t="n">
-        <v>5080</v>
+        <v>3665.39</v>
       </c>
       <c r="F19" t="n">
-        <v>2356.25</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004</v>
+        <v>1.59</v>
       </c>
       <c r="H19" t="n">
-        <v>0.61</v>
+        <v>0.5972</v>
       </c>
       <c r="I19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.8</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.6</v>
-      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.3017</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1272,40 +1212,37 @@
         <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>4338</v>
       </c>
       <c r="E20" t="n">
-        <v>4617</v>
+        <v>3634.27</v>
       </c>
       <c r="F20" t="n">
-        <v>2435.96</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003</v>
+        <v>3.66</v>
       </c>
       <c r="H20" t="n">
-        <v>0.99</v>
+        <v>0.875</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.0083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1315,40 +1252,37 @@
         <v>150</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>5535</v>
       </c>
       <c r="E21" t="n">
-        <v>5919</v>
+        <v>3664.14</v>
       </c>
       <c r="F21" t="n">
-        <v>2411.76</v>
+        <v>0.0005</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003</v>
+        <v>4.59</v>
       </c>
       <c r="H21" t="n">
-        <v>1.24</v>
+        <v>0.875</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8704</v>
+        <v>0.75</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7778</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7013</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1358,40 +1292,37 @@
         <v>300</v>
       </c>
       <c r="D22" t="n">
-        <v>111</v>
+        <v>9989</v>
       </c>
       <c r="E22" t="n">
-        <v>10632</v>
+        <v>3644.17</v>
       </c>
       <c r="F22" t="n">
-        <v>2422.16</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0005</v>
+        <v>7.81</v>
       </c>
       <c r="H22" t="n">
-        <v>2.12</v>
+        <v>0.5444</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5144</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.2429</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1401,40 +1332,37 @@
         <v>50</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>4268</v>
       </c>
       <c r="E23" t="n">
-        <v>4600</v>
+        <v>3661.82</v>
       </c>
       <c r="F23" t="n">
-        <v>2440.02</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004</v>
+        <v>3.6</v>
       </c>
       <c r="H23" t="n">
-        <v>0.54</v>
+        <v>0.8143</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.7143</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8889</v>
+        <v>0.8571</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.7223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1444,40 +1372,37 @@
         <v>150</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>4744</v>
       </c>
       <c r="E24" t="n">
-        <v>5106</v>
+        <v>3701.76</v>
       </c>
       <c r="F24" t="n">
-        <v>2438.07</v>
+        <v>0.0004</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005999999999999999</v>
+        <v>4.07</v>
       </c>
       <c r="H24" t="n">
-        <v>0.59</v>
+        <v>0.663</v>
       </c>
       <c r="I24" t="n">
-        <v>0.77</v>
+        <v>0.5556</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.3085</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1487,40 +1412,37 @@
         <v>300</v>
       </c>
       <c r="D25" t="n">
-        <v>31</v>
+        <v>5744</v>
       </c>
       <c r="E25" t="n">
-        <v>6174</v>
+        <v>3782.05</v>
       </c>
       <c r="F25" t="n">
-        <v>2424.19</v>
+        <v>0.0005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003</v>
+        <v>4.11</v>
       </c>
       <c r="H25" t="n">
-        <v>0.72</v>
+        <v>0.6027</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6183</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.855</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1530,40 +1452,37 @@
         <v>50</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>4274</v>
       </c>
       <c r="E26" t="n">
-        <v>4621</v>
+        <v>3843.11</v>
       </c>
       <c r="F26" t="n">
-        <v>2441.96</v>
+        <v>0.0005</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0008</v>
+        <v>3.54</v>
       </c>
       <c r="H26" t="n">
-        <v>0.53</v>
+        <v>0.591</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.4444</v>
       </c>
       <c r="J26" t="n">
         <v>0.6667</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7778</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.4146</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1573,40 +1492,37 @@
         <v>150</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>4562</v>
       </c>
       <c r="E27" t="n">
-        <v>4952</v>
+        <v>3859.73</v>
       </c>
       <c r="F27" t="n">
-        <v>2423.64</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0005</v>
+        <v>3.86</v>
       </c>
       <c r="H27" t="n">
-        <v>0.39</v>
+        <v>0.5926</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5798</v>
+        <v>0.3333</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7778</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1616,34 +1532,751 @@
         <v>300</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>5116</v>
       </c>
       <c r="E28" t="n">
-        <v>5527</v>
+        <v>3860.37</v>
       </c>
       <c r="F28" t="n">
-        <v>2461.35</v>
+        <v>0.0004</v>
       </c>
       <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7317</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4715</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3868.66</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>500</v>
+      </c>
+      <c r="C30" t="n">
+        <v>150</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6041</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3847.69</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>500</v>
+      </c>
+      <c r="C31" t="n">
+        <v>300</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10854</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3822.49</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>50</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4646</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3852.21</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C33" t="n">
+        <v>150</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5158</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3877.78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C34" t="n">
+        <v>300</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6236</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3871.44</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C35" t="n">
+        <v>50</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4653</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3880.24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6148</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C36" t="n">
+        <v>150</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4984</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3881.83</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6488</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C37" t="n">
+        <v>300</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5563</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3886.43</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>500</v>
+      </c>
+      <c r="C38" t="n">
+        <v>50</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4094</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3893.76</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>500</v>
+      </c>
+      <c r="C39" t="n">
+        <v>150</v>
+      </c>
+      <c r="D39" t="n">
+        <v>5241</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3905.86</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>500</v>
+      </c>
+      <c r="C40" t="n">
+        <v>300</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9428</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3887.44</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5833</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4025</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3884.55</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7262</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C42" t="n">
+        <v>150</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4469</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3877.34</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C43" t="n">
+        <v>300</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5395</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3913.36</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C44" t="n">
+        <v>50</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4032</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3913.19</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.0003</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="G44" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6706</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C45" t="n">
+        <v>150</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4310</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3860.84</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7566000000000001</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C46" t="n">
+        <v>300</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4817</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3857.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.3421</v>
+      <c r="J46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1657,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1678,50 +2311,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nº Chunks</t>
+          <t>Total Tokens</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total Tokens</t>
+          <t>RAM (MB)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>RAM Proceso (MB)</t>
+          <t>T. Chunking (s)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tiempo Chunking (s)</t>
+          <t>T. Embedding (s)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Tiempo Embedding (s)</t>
+          <t>MRR</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>MRR</t>
+          <t>Top_1_Acc</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Top_1_Accuracy</t>
+          <t>Top_3_Acc</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Top_3_Accuracy</t>
+          <t>LLM_Judge</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>LLM_Judge_Score</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>Eficiencia (MRR / T.Emb)</t>
         </is>
@@ -1730,170 +2358,201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-base</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>166.6666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>5396.666666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>4617</v>
+        <v>3739.046666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>2435.96</v>
+        <v>0.0005222222222222222</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003</v>
+        <v>4.36</v>
       </c>
       <c r="H2" t="n">
-        <v>0.99</v>
+        <v>0.6988555555555556</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.5497333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.7964777777777778</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.0083</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MRR</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Top_3_Accuracy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>LLM_Judge_Score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tiempo Embedding (s)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Total Tokens</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RAM Proceso (MB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>intfloat/multilingual-e5-small</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.8103666666666667</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9543222222222223</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.6344444444444445</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5318.666666666667</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2399.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+          <t>intfloat/multilingual-e5-small</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7350444444444445</v>
+        <v>1000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7864222222222222</v>
+        <v>166.6666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>5396.666666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8388888888888889</v>
+        <v>3595.786666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>5794.222222222223</v>
+        <v>0.0005111111111111111</v>
       </c>
       <c r="G3" t="n">
-        <v>2461.35</v>
+        <v>2.081111111111111</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6586</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5113333333333334</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7679555555555555</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>sentence-transformers/LaBSE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>166.6666666666667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5090.111111111111</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3888.171111111111</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0004333333333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.444444444444445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7277666666666667</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5749222222222222</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8322777777777778</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sentence-transformers/distiluse-base-multilingual-cased-v1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>166.6666666666667</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5872.222222222223</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3865.418888888888</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.771111111111111</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6253333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4525555555555556</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7758444444444444</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>sentence-transformers/paraphrase-multilingual-MiniLM-L12-v2</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.6442555555555556</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7839555555555555</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4122222222222222</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5318.666666666667</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2296.12</v>
+      <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>166.6666666666667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5396.666666666667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3542.924444444444</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9077777777777778</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5942666666666666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4497777777777778</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6809222222222222</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
   </sheetData>
